--- a/output/pdf_financials_xlsx/KSM.xlsx
+++ b/output/pdf_financials_xlsx/KSM.xlsx
@@ -1637,10 +1637,10 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.90473</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.865709</v>
       </c>
     </row>
     <row r="93">
@@ -2664,7 +2664,11 @@
           <t>Reserves (note 6)</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E16" s="5" t="n">
         <v>0.90473</v>
       </c>

--- a/output/pdf_financials_xlsx/KSM.xlsx
+++ b/output/pdf_financials_xlsx/KSM.xlsx
@@ -579,10 +579,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.011284</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.024443</v>
       </c>
     </row>
     <row r="13">
@@ -782,10 +782,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.281726</v>
+        <v>-0.29301</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.538459</v>
+        <v>-0.562902</v>
       </c>
     </row>
     <row r="28">
@@ -808,10 +808,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.281726</v>
+        <v>-0.29301</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.538459</v>
+        <v>-0.562902</v>
       </c>
     </row>
     <row r="30">
@@ -875,10 +875,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.391978</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.6493719999999999</v>
       </c>
     </row>
     <row r="35">
@@ -901,10 +901,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.391978</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.5</v>
+        <v>1.149372</v>
       </c>
     </row>
     <row r="37">
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.450826</v>
+        <v>0.058848</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.702724</v>
+        <v>0.053352</v>
       </c>
     </row>
     <row r="49">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -3574,7 +3574,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E49" s="5" t="n">

--- a/output/pdf_financials_xlsx/KSM.xlsx
+++ b/output/pdf_financials_xlsx/KSM.xlsx
@@ -1748,10 +1748,10 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>0.002086</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>-0.011877</v>
+        <v>-0.009476</v>
       </c>
     </row>
     <row r="102">
@@ -1813,10 +1813,10 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0.084518</v>
+        <v>0.086604</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>-0.108989</v>
+        <v>-0.106588</v>
       </c>
     </row>
     <row r="107">
@@ -2828,7 +2828,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E22" s="5" t="n">
         <v>0.002086</v>
       </c>
